--- a/artfynd/A 2011-2023 artfynd.xlsx
+++ b/artfynd/A 2011-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113679528</v>
+        <v>113679529</v>
       </c>
       <c r="B2" t="n">
-        <v>79290</v>
+        <v>79265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637628</v>
+        <v>637630</v>
       </c>
       <c r="R2" t="n">
         <v>7054217</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680910</v>
+        <v>113679531</v>
       </c>
       <c r="B3" t="n">
-        <v>90148</v>
+        <v>77953</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637687</v>
+        <v>637677</v>
       </c>
       <c r="R3" t="n">
-        <v>7054063</v>
+        <v>7054076</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,12 +873,12 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW3" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113679529</v>
+        <v>113680910</v>
       </c>
       <c r="B4" t="n">
-        <v>79263</v>
+        <v>90150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637630</v>
+        <v>637687</v>
       </c>
       <c r="R4" t="n">
-        <v>7054217</v>
+        <v>7054063</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,12 +984,12 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113679531</v>
+        <v>113679530</v>
       </c>
       <c r="B5" t="n">
-        <v>77951</v>
+        <v>78768</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637677</v>
+        <v>637676</v>
       </c>
       <c r="R5" t="n">
-        <v>7054076</v>
+        <v>7054073</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113679530</v>
+        <v>113679528</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>79292</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637676</v>
+        <v>637628</v>
       </c>
       <c r="R6" t="n">
-        <v>7054073</v>
+        <v>7054217</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 2011-2023 artfynd.xlsx
+++ b/artfynd/A 2011-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113679529</v>
+        <v>113679530</v>
       </c>
       <c r="B2" t="n">
-        <v>79265</v>
+        <v>78768</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637630</v>
+        <v>637676</v>
       </c>
       <c r="R2" t="n">
-        <v>7054217</v>
+        <v>7054073</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113680910</v>
+        <v>113679528</v>
       </c>
       <c r="B4" t="n">
-        <v>90150</v>
+        <v>79292</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637687</v>
+        <v>637628</v>
       </c>
       <c r="R4" t="n">
-        <v>7054063</v>
+        <v>7054217</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,12 +984,12 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW4" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113679530</v>
+        <v>113680910</v>
       </c>
       <c r="B5" t="n">
-        <v>78768</v>
+        <v>90151</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637676</v>
+        <v>637687</v>
       </c>
       <c r="R5" t="n">
-        <v>7054073</v>
+        <v>7054063</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,12 +1095,12 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113679528</v>
+        <v>113679529</v>
       </c>
       <c r="B6" t="n">
-        <v>79292</v>
+        <v>79265</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637628</v>
+        <v>637630</v>
       </c>
       <c r="R6" t="n">
         <v>7054217</v>

--- a/artfynd/A 2011-2023 artfynd.xlsx
+++ b/artfynd/A 2011-2023 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113679528</v>
+        <v>113680910</v>
       </c>
       <c r="B4" t="n">
-        <v>79292</v>
+        <v>90155</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637628</v>
+        <v>637687</v>
       </c>
       <c r="R4" t="n">
-        <v>7054217</v>
+        <v>7054063</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,12 +984,12 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113680910</v>
+        <v>113679529</v>
       </c>
       <c r="B5" t="n">
-        <v>90151</v>
+        <v>79265</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637687</v>
+        <v>637630</v>
       </c>
       <c r="R5" t="n">
-        <v>7054063</v>
+        <v>7054217</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,12 +1095,12 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW5" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113679529</v>
+        <v>113679528</v>
       </c>
       <c r="B6" t="n">
-        <v>79265</v>
+        <v>79292</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637630</v>
+        <v>637628</v>
       </c>
       <c r="R6" t="n">
         <v>7054217</v>

--- a/artfynd/A 2011-2023 artfynd.xlsx
+++ b/artfynd/A 2011-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113679530</v>
+        <v>113679529</v>
       </c>
       <c r="B2" t="n">
-        <v>78768</v>
+        <v>79265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637676</v>
+        <v>637630</v>
       </c>
       <c r="R2" t="n">
-        <v>7054073</v>
+        <v>7054217</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113679531</v>
+        <v>113680910</v>
       </c>
       <c r="B3" t="n">
-        <v>77953</v>
+        <v>90155</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637677</v>
+        <v>637687</v>
       </c>
       <c r="R3" t="n">
-        <v>7054076</v>
+        <v>7054063</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,12 +873,12 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113680910</v>
+        <v>113679531</v>
       </c>
       <c r="B4" t="n">
-        <v>90155</v>
+        <v>77953</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637687</v>
+        <v>637677</v>
       </c>
       <c r="R4" t="n">
-        <v>7054063</v>
+        <v>7054076</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,12 +984,12 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW4" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113679529</v>
+        <v>113679530</v>
       </c>
       <c r="B5" t="n">
-        <v>79265</v>
+        <v>78768</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637630</v>
+        <v>637676</v>
       </c>
       <c r="R5" t="n">
-        <v>7054217</v>
+        <v>7054073</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 2011-2023 artfynd.xlsx
+++ b/artfynd/A 2011-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113679529</v>
+        <v>113679528</v>
       </c>
       <c r="B2" t="n">
-        <v>79265</v>
+        <v>79292</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637630</v>
+        <v>637628</v>
       </c>
       <c r="R2" t="n">
         <v>7054217</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680910</v>
+        <v>113679530</v>
       </c>
       <c r="B3" t="n">
-        <v>90155</v>
+        <v>78768</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637687</v>
+        <v>637676</v>
       </c>
       <c r="R3" t="n">
-        <v>7054063</v>
+        <v>7054073</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,12 +873,12 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW3" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113679530</v>
+        <v>113679529</v>
       </c>
       <c r="B5" t="n">
-        <v>78768</v>
+        <v>79265</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637676</v>
+        <v>637630</v>
       </c>
       <c r="R5" t="n">
-        <v>7054073</v>
+        <v>7054217</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113679528</v>
+        <v>113680910</v>
       </c>
       <c r="B6" t="n">
-        <v>79292</v>
+        <v>90155</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637628</v>
+        <v>637687</v>
       </c>
       <c r="R6" t="n">
-        <v>7054217</v>
+        <v>7054063</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,12 +1206,12 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
           <t>Helene Andersson</t>

--- a/artfynd/A 2011-2023 artfynd.xlsx
+++ b/artfynd/A 2011-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113679528</v>
+        <v>113679530</v>
       </c>
       <c r="B2" t="n">
-        <v>79292</v>
+        <v>78768</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637628</v>
+        <v>637676</v>
       </c>
       <c r="R2" t="n">
-        <v>7054217</v>
+        <v>7054073</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113679530</v>
+        <v>113679529</v>
       </c>
       <c r="B3" t="n">
-        <v>78768</v>
+        <v>79265</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637676</v>
+        <v>637630</v>
       </c>
       <c r="R3" t="n">
-        <v>7054073</v>
+        <v>7054217</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113679529</v>
+        <v>113680910</v>
       </c>
       <c r="B5" t="n">
-        <v>79265</v>
+        <v>90155</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637630</v>
+        <v>637687</v>
       </c>
       <c r="R5" t="n">
-        <v>7054217</v>
+        <v>7054063</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,12 +1095,12 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113680910</v>
+        <v>113679528</v>
       </c>
       <c r="B6" t="n">
-        <v>90155</v>
+        <v>79292</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637687</v>
+        <v>637628</v>
       </c>
       <c r="R6" t="n">
-        <v>7054063</v>
+        <v>7054217</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,12 +1206,12 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW6" t="inlineStr">
         <is>
           <t>Helene Andersson</t>

--- a/artfynd/A 2011-2023 artfynd.xlsx
+++ b/artfynd/A 2011-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113679530</v>
+        <v>113680910</v>
       </c>
       <c r="B2" t="n">
-        <v>78768</v>
+        <v>90155</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637676</v>
+        <v>637687</v>
       </c>
       <c r="R2" t="n">
-        <v>7054073</v>
+        <v>7054063</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,12 +762,12 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113679529</v>
+        <v>113679528</v>
       </c>
       <c r="B3" t="n">
-        <v>79265</v>
+        <v>79292</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637630</v>
+        <v>637628</v>
       </c>
       <c r="R3" t="n">
         <v>7054217</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113680910</v>
+        <v>113679529</v>
       </c>
       <c r="B5" t="n">
-        <v>90155</v>
+        <v>79265</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637687</v>
+        <v>637630</v>
       </c>
       <c r="R5" t="n">
-        <v>7054063</v>
+        <v>7054217</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,12 +1095,12 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW5" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113679528</v>
+        <v>113679530</v>
       </c>
       <c r="B6" t="n">
-        <v>79292</v>
+        <v>78768</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637628</v>
+        <v>637676</v>
       </c>
       <c r="R6" t="n">
-        <v>7054217</v>
+        <v>7054073</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 2011-2023 artfynd.xlsx
+++ b/artfynd/A 2011-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2011-2023 artfynd.xlsx
+++ b/artfynd/A 2011-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>113679530</v>
       </c>
       <c r="B2" t="n">
-        <v>79074</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,12 +770,12 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -789,12 +784,7 @@
         <v>113680910</v>
       </c>
       <c r="B3" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,12 +876,12 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -900,12 +890,7 @@
         <v>113679531</v>
       </c>
       <c r="B4" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,12 +982,12 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -1011,12 +996,7 @@
         <v>113679528</v>
       </c>
       <c r="B5" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,12 +1088,12 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -1122,12 +1102,7 @@
         <v>113679533</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79310</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,12 +1194,12 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -1233,12 +1208,7 @@
         <v>113679529</v>
       </c>
       <c r="B7" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,12 +1300,12 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 2011-2023 artfynd.xlsx
+++ b/artfynd/A 2011-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679530</v>
       </c>
       <c r="B2" t="n">
-        <v>79905</v>
+        <v>79907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113680910</v>
       </c>
       <c r="B3" t="n">
-        <v>91910</v>
+        <v>91913</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113679531</v>
       </c>
       <c r="B4" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>113679528</v>
       </c>
       <c r="B5" t="n">
-        <v>80449</v>
+        <v>80451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>113679533</v>
       </c>
       <c r="B6" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>113679529</v>
       </c>
       <c r="B7" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 2011-2023 artfynd.xlsx
+++ b/artfynd/A 2011-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679530</v>
       </c>
       <c r="B2" t="n">
-        <v>79907</v>
+        <v>79909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113680910</v>
       </c>
       <c r="B3" t="n">
-        <v>91913</v>
+        <v>91919</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113679531</v>
       </c>
       <c r="B4" t="n">
-        <v>79074</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>113679528</v>
       </c>
       <c r="B5" t="n">
-        <v>80451</v>
+        <v>80453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>113679533</v>
       </c>
       <c r="B6" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>113679529</v>
       </c>
       <c r="B7" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 2011-2023 artfynd.xlsx
+++ b/artfynd/A 2011-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679530</v>
       </c>
       <c r="B2" t="n">
-        <v>79909</v>
+        <v>79917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113680910</v>
       </c>
       <c r="B3" t="n">
-        <v>91919</v>
+        <v>91929</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113679531</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>113679528</v>
       </c>
       <c r="B5" t="n">
-        <v>80453</v>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>113679533</v>
       </c>
       <c r="B6" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>113679529</v>
       </c>
       <c r="B7" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 2011-2023 artfynd.xlsx
+++ b/artfynd/A 2011-2023 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>113680910</v>
       </c>
       <c r="B3" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2011-2023 artfynd.xlsx
+++ b/artfynd/A 2011-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680910</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679533</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679531</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679529</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679528</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113682775</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,8 +1449,22 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679530</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>